--- a/output/xlsx/VisualizarEEditarConta--GT-.xlsx
+++ b/output/xlsx/VisualizarEEditarConta--GT-.xlsx
@@ -98,7 +98,7 @@
     <t/>
   </si>
   <si>
-    <t>SYSTEM exibe tela onde os campos 'Name', 'Login', 'Type', 'Laboratory' e 'Language'. Eles estão devidamente preenchidos</t>
+    <t>SYSTEM exibe tela onde os campos 'Name', 'Login', 'Type' e 'Language'. Eles estão devidamente preenchidos</t>
   </si>
   <si>
     <t>operador: pressiona botao 'Edit'</t>
